--- a/employment_forms/021_recruitment_application_form--employment_forms.xlsx
+++ b/employment_forms/021_recruitment_application_form--employment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -826,8 +826,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -855,12 +855,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'junior_developer',_'value':_'junior_developer'}</t>
+          <t>junior_developer</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'Junior Developer', 'value': 'Junior Developer'}</t>
+          <t>Junior Developer</t>
         </is>
       </c>
     </row>
@@ -872,12 +872,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'senior_developer',_'value':_'senior_developer'}</t>
+          <t>senior_developer</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'Senior Developer', 'value': 'Senior Developer'}</t>
+          <t>Senior Developer</t>
         </is>
       </c>
     </row>
@@ -889,12 +889,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'very_satisfied',_'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'Very Satisfied', 'value': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -906,12 +906,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'id':_13,_'name':_'somewhat_satisfied',_'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'id': 13, 'name': 'Somewhat Satisfied', 'value': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -923,12 +923,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'id':_14,_'name':_'neutral',_'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'id': 14, 'name': 'Neutral', 'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -940,12 +940,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'id':_15,_'name':_'somewhat_dissatisfied',_'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'id': 15, 'name': 'Somewhat Dissatisfied', 'value': 'Somewhat Dissatisfied'}</t>
+          <t>Somewhat Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -957,12 +957,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'id':_16,_'name':_'very_dissatisfied',_'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'id': 16, 'name': 'Very Dissatisfied', 'value': 'Very Dissatisfied'}</t>
+          <t>Very Dissatisfied</t>
         </is>
       </c>
     </row>
@@ -974,12 +974,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'id':_17,_'name':_'english',_'value':_'english'}</t>
+          <t>english</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'id': 17, 'name': 'English', 'value': 'English'}</t>
+          <t>English</t>
         </is>
       </c>
     </row>
@@ -991,12 +991,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_18,_'name':_'spanish',_'value':_'spanish'}</t>
+          <t>spanish</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 18, 'name': 'Spanish', 'value': 'Spanish'}</t>
+          <t>Spanish</t>
         </is>
       </c>
     </row>
@@ -1008,12 +1008,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_19,_'name':_'french',_'value':_'french'}</t>
+          <t>french</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 19, 'name': 'French', 'value': 'French'}</t>
+          <t>French</t>
         </is>
       </c>
     </row>
@@ -1025,12 +1025,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_20,_'name':_'arabic',_'value':_'arabic'}</t>
+          <t>arabic</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 20, 'name': 'Arabic', 'value': 'Arabic'}</t>
+          <t>Arabic</t>
         </is>
       </c>
     </row>
@@ -1042,12 +1042,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_21,_'name':_'html',_'value':_'html'}</t>
+          <t>html</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 21, 'name': 'Html', 'value': 'Html'}</t>
+          <t>Html</t>
         </is>
       </c>
     </row>
@@ -1059,12 +1059,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_22,_'name':_'css',_'value':_'css'}</t>
+          <t>css</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 22, 'name': 'Css', 'value': 'Css'}</t>
+          <t>Css</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_23,_'name':_'javascript',_'value':_'javascript'}</t>
+          <t>javascript</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 23, 'name': 'JavaScript', 'value': 'JavaScript'}</t>
+          <t>JavaScript</t>
         </is>
       </c>
     </row>
@@ -1093,12 +1093,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_24,_'name':_'python',_'value':_'python'}</t>
+          <t>python</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 24, 'name': 'Python', 'value': 'Python'}</t>
+          <t>Python</t>
         </is>
       </c>
     </row>
